--- a/artfynd/A 38141-2024 artfynd.xlsx
+++ b/artfynd/A 38141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820097</v>
+        <v>119820098</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820099</v>
+        <v>119820097</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>78263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>476740</v>
       </c>
       <c r="R3" t="n">
-        <v>6838684</v>
+        <v>6838682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820098</v>
+        <v>119820099</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>79115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>476740</v>
       </c>
       <c r="R4" t="n">
-        <v>6838682</v>
+        <v>6838684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38141-2024 artfynd.xlsx
+++ b/artfynd/A 38141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820098</v>
+        <v>119820097</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820097</v>
+        <v>119820099</v>
       </c>
       <c r="B3" t="n">
-        <v>78263</v>
+        <v>79115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>476740</v>
       </c>
       <c r="R3" t="n">
-        <v>6838682</v>
+        <v>6838684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820099</v>
+        <v>119820098</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>78262</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +944,7 @@
         <v>476740</v>
       </c>
       <c r="R4" t="n">
-        <v>6838684</v>
+        <v>6838682</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 38141-2024 artfynd.xlsx
+++ b/artfynd/A 38141-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119820097</v>
       </c>
       <c r="B2" t="n">
-        <v>78263</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>119820099</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>119820098</v>
       </c>
       <c r="B4" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 38141-2024 artfynd.xlsx
+++ b/artfynd/A 38141-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119820097</v>
+        <v>119820099</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>79131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,7 +722,7 @@
         <v>476740</v>
       </c>
       <c r="R2" t="n">
-        <v>6838682</v>
+        <v>6838684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119820099</v>
+        <v>119820098</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,7 +833,7 @@
         <v>476740</v>
       </c>
       <c r="R3" t="n">
-        <v>6838684</v>
+        <v>6838682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820098</v>
+        <v>119820097</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
